--- a/engagement_survey_forms/005_social_justice_metrics_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/005_social_justice_metrics_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'very_high'}</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'fairly_high'}</t>
+          <t>fairly_high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'fairly_high'}</t>
+          <t>fairly high</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_high'}</t>
+          <t>somewhat_high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_high'}</t>
+          <t>somewhat high</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'not_at_all'}</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_inclusive'}</t>
+          <t>very_inclusive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'very_inclusive'}</t>
+          <t>very inclusive</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'fairly_inclusive'}</t>
+          <t>fairly_inclusive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'fairly_inclusive'}</t>
+          <t>fairly inclusive</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_inclusive'}</t>
+          <t>somewhat_inclusive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_inclusive'}</t>
+          <t>somewhat inclusive</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'very_exclusive'}</t>
+          <t>very_exclusive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'very_exclusive'}</t>
+          <t>very exclusive</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'very_strongly_belong'}</t>
+          <t>very_strongly_belong</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'very_strongly_belong'}</t>
+          <t>very strongly belong</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_belong'}</t>
+          <t>somewhat_belong</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_belong'}</t>
+          <t>somewhat belong</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'not_at_all'}</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'advocacy'}</t>
+          <t>advocacy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'advocacy'}</t>
+          <t>advocacy</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'education'}</t>
+          <t>education</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'ally'}</t>
+          <t>ally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'ally'}</t>
+          <t>ally</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'support'}</t>
+          <t>support</t>
         </is>
       </c>
     </row>
